--- a/DateBase/orders/Nha Thu_2026-9-12.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-12.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0510169120109150</v>
+        <v>0510169120109157</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-12.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,89 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>693_迎客豆_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>441_蓝星球_Echinops_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>525_栀子果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>772_格桑花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>518_多头鼠尾 紫色_spray veronica purple_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0510169120109157</v>
+        <v>0510169120109157105101020551050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-12.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-12.xlsx
@@ -604,6 +604,9 @@
       <c r="C21" t="str">
         <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -662,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0510169120109157105101020551050</v>
+        <v>0510169120109157105101020551055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-12.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -608,9 +608,44 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -665,7 +700,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0510169120109157105101020551055</v>
+        <v>05101691201091571051010205510559665</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-12.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+        <v>640_红辣椒_undefined_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
         <v>5</v>
@@ -451,201 +451,42 @@
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+        <v>442_僵尸果（进口）_undefined_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+        <v>431_小米果_undefined_undefined_1bunch</v>
       </c>
       <c r="F4" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="str">
+        <v>2</v>
+      </c>
       <c r="C5" t="str">
-        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+        <v>864_黄洋金边红色_undefined_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+        <v>877_黄洋金边原色_undefined_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="C7" t="str" xml:space="preserve">
-        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
-white_Trachymene Coerulea_1bunch</v>
-      </c>
-      <c r="F7" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F8" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F9" t="str">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="str">
-        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F10" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="str">
-        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F11" t="str">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="str">
-        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F12" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>3</v>
-      </c>
-      <c r="C13" t="str">
-        <v>693_迎客豆_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F13" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="str">
-        <v>436_木百合_leucadendron _undefined_1bunch</v>
-      </c>
-      <c r="F14" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" t="str">
-        <v>441_蓝星球_Echinops_undefined_1bunch</v>
-      </c>
-      <c r="F15" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="str">
-        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="str">
-        <v>525_栀子果_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F17" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
-      </c>
-      <c r="F18" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>772_格桑花粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F19" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="str">
-        <v>518_多头鼠尾 紫色_spray veronica purple_undefined_1bunch</v>
-      </c>
-      <c r="F20" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F21" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>4</v>
-      </c>
-      <c r="C22" t="str">
-        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F22" t="str">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="str">
-        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F23" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F24" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="str">
-        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F25" t="str">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -700,7 +541,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05101691201091571051010205510559665</v>
+        <v>0552055</v>
       </c>
     </row>
   </sheetData>
